--- a/TS2_mapping.xlsx
+++ b/TS2_mapping.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="195">
   <si>
     <t>BUILD</t>
   </si>
@@ -63,9 +63,6 @@
     <t>FAIL</t>
   </si>
   <si>
-    <t>FAIl</t>
-  </si>
-  <si>
     <t>63265142550005</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -775,6 +772,14 @@
   </si>
   <si>
     <t>63265142450007</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>63765155580008</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>63765155580007</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1077,18 +1082,102 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1097,90 +1186,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1486,69 +1491,70 @@
   <dimension ref="A1:H71"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="34.33203125" style="41" customWidth="1"/>
+    <col min="3" max="3" width="34.33203125" style="29" customWidth="1"/>
     <col min="4" max="4" width="23.33203125" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="7" max="7" width="23.77734375" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="39" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="35" t="s">
+      <c r="A2" s="31"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="26"/>
-      <c r="E2" s="10" t="s">
+      <c r="D2" s="34"/>
+      <c r="E2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="29"/>
-      <c r="G2" s="12" t="s">
+      <c r="F2" s="37"/>
+      <c r="G2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="32"/>
+      <c r="H2" s="40"/>
     </row>
     <row r="3" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="35" t="s">
+      <c r="A3" s="32"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="27"/>
-      <c r="E3" s="10" t="s">
+      <c r="D3" s="35"/>
+      <c r="E3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="30"/>
-      <c r="G3" s="13" t="s">
+      <c r="F3" s="38"/>
+      <c r="G3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="33"/>
+      <c r="H3" s="41"/>
     </row>
     <row r="4" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1557,22 +1563,22 @@
       <c r="B4" s="1">
         <v>2</v>
       </c>
-      <c r="C4" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="36" t="s">
-        <v>76</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="H4" s="15" t="s">
+      <c r="C4" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="H4" s="13" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1583,22 +1589,22 @@
       <c r="B5" s="3">
         <v>4</v>
       </c>
-      <c r="C5" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="38" t="s">
-        <v>134</v>
-      </c>
-      <c r="H5" s="17" t="s">
+      <c r="C5" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="H5" s="15" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1609,22 +1615,22 @@
       <c r="B6" s="3">
         <v>5</v>
       </c>
-      <c r="C6" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="38" t="s">
-        <v>193</v>
-      </c>
-      <c r="H6" s="18" t="s">
+      <c r="C6" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="H6" s="16" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1635,22 +1641,22 @@
       <c r="B7" s="3">
         <v>7</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="D7" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="38" t="s">
-        <v>175</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="H7" s="18" t="s">
+      <c r="F7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="H7" s="16" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1661,22 +1667,22 @@
       <c r="B8" s="4">
         <v>11</v>
       </c>
-      <c r="C8" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="38" t="s">
-        <v>136</v>
-      </c>
-      <c r="H8" s="18" t="s">
+      <c r="C8" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="H8" s="16" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1687,23 +1693,23 @@
       <c r="B9" s="4">
         <v>12</v>
       </c>
-      <c r="C9" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="38" t="s">
-        <v>137</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>14</v>
+      <c r="C9" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1713,22 +1719,22 @@
       <c r="B10" s="5">
         <v>16</v>
       </c>
-      <c r="C10" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="39" t="s">
-        <v>138</v>
-      </c>
-      <c r="H10" s="20" t="s">
+      <c r="C10" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="H10" s="18" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1739,22 +1745,22 @@
       <c r="B11" s="5">
         <v>17</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="D11" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="39" t="s">
+      <c r="F11" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="F11" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="39" t="s">
-        <v>178</v>
-      </c>
-      <c r="H11" s="20" t="s">
+      <c r="H11" s="18" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1765,22 +1771,22 @@
       <c r="B12" s="2">
         <v>21</v>
       </c>
-      <c r="C12" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="38" t="s">
-        <v>139</v>
-      </c>
-      <c r="H12" s="18" t="s">
+      <c r="C12" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="H12" s="16" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1791,22 +1797,22 @@
       <c r="B13" s="5">
         <v>23</v>
       </c>
-      <c r="C13" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="39" t="s">
-        <v>83</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="39" t="s">
-        <v>140</v>
-      </c>
-      <c r="H13" s="21" t="s">
+      <c r="C13" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="H13" s="19" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1817,22 +1823,24 @@
       <c r="B14" s="5">
         <v>24</v>
       </c>
-      <c r="C14" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="39" t="s">
-        <v>141</v>
-      </c>
-      <c r="H14" s="22"/>
+      <c r="C14" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
@@ -1841,22 +1849,22 @@
       <c r="B15" s="5">
         <v>27</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="D15" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="39" t="s">
+      <c r="F15" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="F15" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="39" t="s">
-        <v>186</v>
-      </c>
-      <c r="H15" s="20" t="s">
+      <c r="H15" s="18" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1867,22 +1875,22 @@
       <c r="B16" s="5">
         <v>28</v>
       </c>
-      <c r="C16" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="39" t="s">
-        <v>142</v>
-      </c>
-      <c r="H16" s="20" t="s">
+      <c r="C16" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="H16" s="18" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1893,22 +1901,22 @@
       <c r="B17" s="2">
         <v>29</v>
       </c>
-      <c r="C17" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="F17" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="H17" s="17" t="s">
+      <c r="C17" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="H17" s="15" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1919,22 +1927,22 @@
       <c r="B18" s="5">
         <v>30</v>
       </c>
-      <c r="C18" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="H18" s="21" t="s">
+      <c r="C18" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="H18" s="19" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1945,22 +1953,22 @@
       <c r="B19" s="5">
         <v>33</v>
       </c>
-      <c r="C19" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="39" t="s">
-        <v>91</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="39" t="s">
-        <v>145</v>
-      </c>
-      <c r="H19" s="22"/>
+      <c r="C19" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="H19" s="20"/>
     </row>
     <row r="20" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
@@ -1969,22 +1977,22 @@
       <c r="B20" s="5">
         <v>34</v>
       </c>
-      <c r="C20" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="F20" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="39" t="s">
-        <v>146</v>
-      </c>
-      <c r="H20" s="20" t="s">
+      <c r="C20" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="H20" s="18" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1995,22 +2003,22 @@
       <c r="B21" s="5">
         <v>35</v>
       </c>
-      <c r="C21" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="39" t="s">
-        <v>93</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="39" t="s">
-        <v>147</v>
-      </c>
-      <c r="H21" s="22"/>
+      <c r="C21" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="H21" s="20"/>
     </row>
     <row r="22" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
@@ -2019,22 +2027,22 @@
       <c r="B22" s="2">
         <v>36</v>
       </c>
-      <c r="C22" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="F22" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="38" t="s">
-        <v>149</v>
-      </c>
-      <c r="H22" s="18" t="s">
+      <c r="C22" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="H22" s="16" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2045,22 +2053,22 @@
       <c r="B23" s="5">
         <v>37</v>
       </c>
-      <c r="C23" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="39" t="s">
-        <v>94</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="H23" s="20" t="s">
+      <c r="C23" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="H23" s="18" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2071,22 +2079,22 @@
       <c r="B24" s="5">
         <v>38</v>
       </c>
-      <c r="C24" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="F24" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="39" t="s">
-        <v>150</v>
-      </c>
-      <c r="H24" s="20" t="s">
+      <c r="C24" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="H24" s="18" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2097,22 +2105,22 @@
       <c r="B25" s="5">
         <v>41</v>
       </c>
-      <c r="C25" s="39" t="s">
+      <c r="C25" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="D25" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="39" t="s">
+      <c r="F25" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="27" t="s">
         <v>182</v>
       </c>
-      <c r="F25" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" s="39" t="s">
-        <v>183</v>
-      </c>
-      <c r="H25" s="18" t="s">
+      <c r="H25" s="16" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2123,22 +2131,24 @@
       <c r="B26" s="5">
         <v>43</v>
       </c>
-      <c r="C26" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="39" t="s">
-        <v>96</v>
-      </c>
-      <c r="F26" s="23" t="s">
+      <c r="C26" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="H26" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G26" s="39" t="s">
-        <v>96</v>
-      </c>
-      <c r="H26" s="22"/>
     </row>
     <row r="27" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
@@ -2147,22 +2157,24 @@
       <c r="B27" s="5">
         <v>44</v>
       </c>
-      <c r="C27" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="39" t="s">
-        <v>97</v>
-      </c>
-      <c r="F27" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="H27" s="22"/>
+      <c r="C27" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="F27" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="28" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
@@ -2171,22 +2183,22 @@
       <c r="B28" s="5">
         <v>47</v>
       </c>
-      <c r="C28" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="F28" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="H28" s="20" t="s">
+      <c r="C28" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="H28" s="18" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2197,22 +2209,22 @@
       <c r="B29" s="5">
         <v>48</v>
       </c>
-      <c r="C29" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="F29" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" s="39" t="s">
-        <v>153</v>
-      </c>
-      <c r="H29" s="21" t="s">
+      <c r="C29" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="H29" s="19" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2223,22 +2235,22 @@
       <c r="B30" s="2">
         <v>49</v>
       </c>
-      <c r="C30" s="40" t="s">
-        <v>38</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" s="38" t="s">
-        <v>100</v>
-      </c>
-      <c r="F30" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="38" t="s">
-        <v>154</v>
-      </c>
-      <c r="H30" s="17" t="s">
+      <c r="C30" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="H30" s="15" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2249,22 +2261,22 @@
       <c r="B31" s="5">
         <v>51</v>
       </c>
-      <c r="C31" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="39" t="s">
-        <v>101</v>
-      </c>
-      <c r="F31" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="H31" s="21" t="s">
+      <c r="C31" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="H31" s="19" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2275,20 +2287,20 @@
       <c r="B32" s="5">
         <v>52</v>
       </c>
-      <c r="C32" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E32" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="39"/>
-      <c r="H32" s="22"/>
+      <c r="C32" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="27"/>
+      <c r="H32" s="20"/>
     </row>
     <row r="33" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
@@ -2297,22 +2309,22 @@
       <c r="B33" s="5">
         <v>53</v>
       </c>
-      <c r="C33" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E33" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="F33" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="H33" s="22"/>
+      <c r="C33" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="H33" s="20"/>
     </row>
     <row r="34" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
@@ -2321,20 +2333,20 @@
       <c r="B34" s="5">
         <v>54</v>
       </c>
-      <c r="C34" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" s="39" t="s">
-        <v>104</v>
-      </c>
-      <c r="F34" s="23" t="s">
+      <c r="C34" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="F34" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G34" s="39"/>
-      <c r="H34" s="22"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="20"/>
     </row>
     <row r="35" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
@@ -2343,22 +2355,22 @@
       <c r="B35" s="5">
         <v>55</v>
       </c>
-      <c r="C35" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="F35" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35" s="39" t="s">
-        <v>157</v>
-      </c>
-      <c r="H35" s="20" t="s">
+      <c r="C35" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="H35" s="18" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2369,22 +2381,22 @@
       <c r="B36" s="5">
         <v>56</v>
       </c>
-      <c r="C36" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" s="39" t="s">
-        <v>106</v>
-      </c>
-      <c r="F36" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="39" t="s">
-        <v>158</v>
-      </c>
-      <c r="H36" s="22"/>
+      <c r="C36" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="F36" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="H36" s="20"/>
     </row>
     <row r="37" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
@@ -2393,22 +2405,22 @@
       <c r="B37" s="5">
         <v>57</v>
       </c>
-      <c r="C37" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="F37" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37" s="39" t="s">
-        <v>159</v>
-      </c>
-      <c r="H37" s="20" t="s">
+      <c r="C37" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="F37" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="H37" s="18" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2419,22 +2431,22 @@
       <c r="B38" s="5">
         <v>58</v>
       </c>
-      <c r="C38" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="F38" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="H38" s="20" t="s">
+      <c r="C38" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="H38" s="18" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2445,22 +2457,22 @@
       <c r="B39" s="5">
         <v>59</v>
       </c>
-      <c r="C39" s="39" t="s">
-        <v>47</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="F39" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" s="39" t="s">
-        <v>161</v>
-      </c>
-      <c r="H39" s="22"/>
+      <c r="C39" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="F39" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="H39" s="20"/>
     </row>
     <row r="40" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
@@ -2469,22 +2481,24 @@
       <c r="B40" s="5">
         <v>60</v>
       </c>
-      <c r="C40" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" s="39" t="s">
-        <v>129</v>
-      </c>
-      <c r="F40" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="G40" s="39" t="s">
-        <v>189</v>
-      </c>
-      <c r="H40" s="22"/>
+      <c r="C40" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="H40" s="17" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="41" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
@@ -2493,20 +2507,24 @@
       <c r="B41" s="5">
         <v>61</v>
       </c>
-      <c r="C41" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D41" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E41" s="39" t="s">
-        <v>131</v>
-      </c>
-      <c r="F41" s="23" t="s">
+      <c r="C41" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="H41" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G41" s="39"/>
-      <c r="H41" s="22"/>
     </row>
     <row r="42" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
@@ -2515,20 +2533,20 @@
       <c r="B42" s="5">
         <v>62</v>
       </c>
-      <c r="C42" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" s="39" t="s">
-        <v>132</v>
-      </c>
-      <c r="F42" s="23" t="s">
+      <c r="C42" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F42" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G42" s="39"/>
-      <c r="H42" s="22"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="20"/>
     </row>
     <row r="43" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
@@ -2537,22 +2555,22 @@
       <c r="B43" s="5">
         <v>64</v>
       </c>
-      <c r="C43" s="39" t="s">
-        <v>51</v>
-      </c>
-      <c r="D43" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E43" s="39" t="s">
-        <v>125</v>
-      </c>
-      <c r="F43" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G43" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="H43" s="20" t="s">
+      <c r="C43" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F43" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="H43" s="18" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2563,22 +2581,24 @@
       <c r="B44" s="5">
         <v>65</v>
       </c>
-      <c r="C44" s="39" t="s">
-        <v>52</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E44" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="F44" s="23" t="s">
+      <c r="C44" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="F44" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G44" s="39" t="s">
-        <v>187</v>
-      </c>
-      <c r="H44" s="22"/>
+      <c r="G44" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="H44" s="17" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="45" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
@@ -2587,22 +2607,22 @@
       <c r="B45" s="5">
         <v>66</v>
       </c>
-      <c r="C45" s="39" t="s">
+      <c r="C45" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="D45" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E45" s="39" t="s">
-        <v>180</v>
-      </c>
-      <c r="F45" s="23" t="s">
+      <c r="F45" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G45" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="H45" s="23" t="s">
+      <c r="G45" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="H45" s="21" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2613,22 +2633,22 @@
       <c r="B46" s="5">
         <v>67</v>
       </c>
-      <c r="C46" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E46" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="F46" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G46" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="H46" s="20" t="s">
+      <c r="C46" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="F46" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="H46" s="18" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2639,18 +2659,20 @@
       <c r="B47" s="5">
         <v>68</v>
       </c>
-      <c r="C47" s="39" t="s">
-        <v>54</v>
-      </c>
-      <c r="D47" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E47" s="39" t="s">
-        <v>108</v>
-      </c>
-      <c r="F47" s="6"/>
-      <c r="G47" s="39"/>
-      <c r="H47" s="22"/>
+      <c r="C47" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="F47" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G47" s="27"/>
+      <c r="H47" s="20"/>
     </row>
     <row r="48" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
@@ -2659,20 +2681,20 @@
       <c r="B48" s="5">
         <v>69</v>
       </c>
-      <c r="C48" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="F48" s="23" t="s">
+      <c r="C48" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="F48" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G48" s="39"/>
-      <c r="H48" s="22"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="20"/>
     </row>
     <row r="49" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
@@ -2681,22 +2703,22 @@
       <c r="B49" s="5">
         <v>70</v>
       </c>
-      <c r="C49" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="D49" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E49" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="F49" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="H49" s="20" t="s">
+      <c r="C49" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="F49" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="H49" s="18" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2707,22 +2729,22 @@
       <c r="B50" s="5">
         <v>71</v>
       </c>
-      <c r="C50" s="39" t="s">
-        <v>56</v>
-      </c>
-      <c r="D50" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="F50" s="23" t="s">
+      <c r="C50" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="F50" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G50" s="39" t="s">
-        <v>190</v>
-      </c>
-      <c r="H50" s="22"/>
+      <c r="G50" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="H50" s="20"/>
     </row>
     <row r="51" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
@@ -2731,22 +2753,22 @@
       <c r="B51" s="5">
         <v>72</v>
       </c>
-      <c r="C51" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="D51" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E51" s="39" t="s">
-        <v>123</v>
-      </c>
-      <c r="F51" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G51" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="H51" s="20" t="s">
+      <c r="C51" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="F51" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="H51" s="18" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2757,20 +2779,24 @@
       <c r="B52" s="5">
         <v>73</v>
       </c>
-      <c r="C52" s="39" t="s">
-        <v>59</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" s="39" t="s">
-        <v>126</v>
-      </c>
-      <c r="F52" s="23" t="s">
+      <c r="C52" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="F52" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="H52" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G52" s="39"/>
-      <c r="H52" s="22"/>
     </row>
     <row r="53" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
@@ -2779,20 +2805,20 @@
       <c r="B53" s="5">
         <v>74</v>
       </c>
-      <c r="C53" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="D53" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E53" s="39" t="s">
-        <v>124</v>
-      </c>
-      <c r="F53" s="23" t="s">
+      <c r="C53" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F53" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G53" s="39"/>
-      <c r="H53" s="22"/>
+      <c r="G53" s="27"/>
+      <c r="H53" s="20"/>
     </row>
     <row r="54" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
@@ -2801,20 +2827,20 @@
       <c r="B54" s="5">
         <v>75</v>
       </c>
-      <c r="C54" s="39" t="s">
-        <v>62</v>
-      </c>
-      <c r="D54" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" s="39" t="s">
-        <v>127</v>
-      </c>
-      <c r="F54" s="23" t="s">
+      <c r="C54" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="F54" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G54" s="39"/>
-      <c r="H54" s="22"/>
+      <c r="G54" s="27"/>
+      <c r="H54" s="20"/>
     </row>
     <row r="55" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
@@ -2823,22 +2849,22 @@
       <c r="B55" s="5">
         <v>76</v>
       </c>
-      <c r="C55" s="39" t="s">
-        <v>61</v>
-      </c>
-      <c r="D55" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E55" s="39" t="s">
-        <v>121</v>
-      </c>
-      <c r="F55" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G55" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="H55" s="22"/>
+      <c r="C55" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="F55" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G55" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="H55" s="20"/>
     </row>
     <row r="56" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
@@ -2847,22 +2873,22 @@
       <c r="B56" s="5">
         <v>77</v>
       </c>
-      <c r="C56" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="D56" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E56" s="39" t="s">
-        <v>120</v>
-      </c>
-      <c r="F56" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56" s="39" t="s">
-        <v>168</v>
-      </c>
-      <c r="H56" s="20" t="s">
+      <c r="C56" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="F56" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="H56" s="18" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2873,22 +2899,22 @@
       <c r="B57" s="5">
         <v>78</v>
       </c>
-      <c r="C57" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="D57" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E57" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="F57" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G57" s="39" t="s">
-        <v>169</v>
-      </c>
-      <c r="H57" s="20" t="s">
+      <c r="C57" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="F57" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="H57" s="18" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2899,22 +2925,24 @@
       <c r="B58" s="5">
         <v>79</v>
       </c>
-      <c r="C58" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="D58" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E58" s="39" t="s">
-        <v>118</v>
-      </c>
-      <c r="F58" s="23" t="s">
+      <c r="C58" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="F58" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="H58" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G58" s="39" t="s">
-        <v>191</v>
-      </c>
-      <c r="H58" s="22"/>
     </row>
     <row r="59" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
@@ -2923,22 +2951,22 @@
       <c r="B59" s="5">
         <v>80</v>
       </c>
-      <c r="C59" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="D59" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="F59" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G59" s="39" t="s">
-        <v>170</v>
-      </c>
-      <c r="H59" s="20" t="s">
+      <c r="C59" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="F59" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="H59" s="18" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2949,14 +2977,14 @@
       <c r="B60" s="5">
         <v>81</v>
       </c>
-      <c r="C60" s="39" t="s">
-        <v>66</v>
+      <c r="C60" s="27" t="s">
+        <v>65</v>
       </c>
       <c r="D60" s="6"/>
-      <c r="E60" s="39"/>
+      <c r="E60" s="27"/>
       <c r="F60" s="6"/>
-      <c r="G60" s="39"/>
-      <c r="H60" s="22"/>
+      <c r="G60" s="27"/>
+      <c r="H60" s="20"/>
     </row>
     <row r="61" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
@@ -2965,22 +2993,24 @@
       <c r="B61" s="5">
         <v>82</v>
       </c>
-      <c r="C61" s="39" t="s">
-        <v>68</v>
-      </c>
-      <c r="D61" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E61" s="39" t="s">
-        <v>116</v>
-      </c>
-      <c r="F61" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G61" s="39" t="s">
-        <v>171</v>
-      </c>
-      <c r="H61" s="22"/>
+      <c r="C61" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="F61" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="H61" s="21" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="62" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
@@ -2989,22 +3019,24 @@
       <c r="B62" s="5">
         <v>83</v>
       </c>
-      <c r="C62" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="D62" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E62" s="39" t="s">
-        <v>115</v>
-      </c>
-      <c r="F62" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G62" s="39" t="s">
-        <v>172</v>
-      </c>
-      <c r="H62" s="22"/>
+      <c r="C62" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="F62" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G62" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="H62" s="21" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="63" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
@@ -3013,12 +3045,12 @@
       <c r="B63" s="5">
         <v>84</v>
       </c>
-      <c r="C63" s="39"/>
+      <c r="C63" s="27"/>
       <c r="D63" s="6"/>
-      <c r="E63" s="39"/>
+      <c r="E63" s="27"/>
       <c r="F63" s="6"/>
-      <c r="G63" s="39"/>
-      <c r="H63" s="22"/>
+      <c r="G63" s="27"/>
+      <c r="H63" s="20"/>
     </row>
     <row r="64" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
@@ -3027,12 +3059,12 @@
       <c r="B64" s="5">
         <v>85</v>
       </c>
-      <c r="C64" s="39"/>
+      <c r="C64" s="27"/>
       <c r="D64" s="6"/>
-      <c r="E64" s="39"/>
+      <c r="E64" s="27"/>
       <c r="F64" s="6"/>
-      <c r="G64" s="39"/>
-      <c r="H64" s="22"/>
+      <c r="G64" s="27"/>
+      <c r="H64" s="20"/>
     </row>
     <row r="65" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
@@ -3041,14 +3073,14 @@
       <c r="B65" s="5">
         <v>86</v>
       </c>
-      <c r="C65" s="39" t="s">
-        <v>70</v>
+      <c r="C65" s="27" t="s">
+        <v>69</v>
       </c>
       <c r="D65" s="6"/>
-      <c r="E65" s="39"/>
+      <c r="E65" s="27"/>
       <c r="F65" s="6"/>
-      <c r="G65" s="39"/>
-      <c r="H65" s="22"/>
+      <c r="G65" s="27"/>
+      <c r="H65" s="20"/>
     </row>
     <row r="66" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
@@ -3057,18 +3089,18 @@
       <c r="B66" s="5">
         <v>87</v>
       </c>
-      <c r="C66" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="D66" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E66" s="39" t="s">
-        <v>114</v>
+      <c r="C66" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="F66" s="6"/>
-      <c r="G66" s="39"/>
-      <c r="H66" s="22"/>
+      <c r="G66" s="27"/>
+      <c r="H66" s="20"/>
     </row>
     <row r="67" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
@@ -3077,22 +3109,22 @@
       <c r="B67" s="5">
         <v>88</v>
       </c>
-      <c r="C67" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="D67" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E67" s="39" t="s">
-        <v>113</v>
-      </c>
-      <c r="F67" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G67" s="39" t="s">
-        <v>173</v>
-      </c>
-      <c r="H67" s="22"/>
+      <c r="C67" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="F67" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="H67" s="20"/>
     </row>
     <row r="68" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
@@ -3101,22 +3133,24 @@
       <c r="B68" s="5">
         <v>89</v>
       </c>
-      <c r="C68" s="39" t="s">
-        <v>73</v>
-      </c>
-      <c r="D68" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E68" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="F68" s="23" t="s">
+      <c r="C68" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="F68" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="H68" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G68" s="39" t="s">
-        <v>192</v>
-      </c>
-      <c r="H68" s="22"/>
     </row>
     <row r="69" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
@@ -3125,20 +3159,20 @@
       <c r="B69" s="5">
         <v>90</v>
       </c>
-      <c r="C69" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="D69" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E69" s="39" t="s">
-        <v>111</v>
+      <c r="C69" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" s="27" t="s">
+        <v>110</v>
       </c>
       <c r="F69" s="6"/>
-      <c r="G69" s="39" t="s">
-        <v>188</v>
-      </c>
-      <c r="H69" s="22"/>
+      <c r="G69" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="H69" s="20"/>
     </row>
     <row r="70" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
@@ -3147,26 +3181,30 @@
       <c r="B70" s="5">
         <v>91</v>
       </c>
-      <c r="C70" s="39" t="s">
-        <v>75</v>
-      </c>
-      <c r="D70" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E70" s="39"/>
+      <c r="C70" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" s="27"/>
       <c r="F70" s="6"/>
-      <c r="G70" s="39"/>
-      <c r="H70" s="22"/>
+      <c r="G70" s="27"/>
+      <c r="H70" s="20"/>
     </row>
     <row r="71" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="A71" s="1"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="39"/>
+      <c r="A71" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B71" s="5">
+        <v>92</v>
+      </c>
+      <c r="C71" s="27"/>
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
-      <c r="H71" s="22"/>
+      <c r="H71" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/TS2_mapping.xlsx
+++ b/TS2_mapping.xlsx
@@ -2250,7 +2250,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">

--- a/TS2_mapping.xlsx
+++ b/TS2_mapping.xlsx
@@ -2292,7 +2292,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">

--- a/TS2_mapping.xlsx
+++ b/TS2_mapping.xlsx
@@ -2470,7 +2470,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>

--- a/TS2_mapping.xlsx
+++ b/TS2_mapping.xlsx
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>無資料</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>

--- a/TS2_mapping.xlsx
+++ b/TS2_mapping.xlsx
@@ -3174,7 +3174,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">

--- a/TS2_mapping.xlsx
+++ b/TS2_mapping.xlsx
@@ -3216,7 +3216,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">

--- a/TS2_mapping.xlsx
+++ b/TS2_mapping.xlsx
@@ -3520,7 +3520,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>

--- a/TS2_mapping.xlsx
+++ b/TS2_mapping.xlsx
@@ -3762,7 +3762,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>無資料</t>
         </is>
       </c>
     </row>

--- a/TS2_mapping.xlsx
+++ b/TS2_mapping.xlsx
@@ -3898,7 +3898,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>

--- a/TS2_mapping.xlsx
+++ b/TS2_mapping.xlsx
@@ -4150,7 +4150,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>

--- a/TS2_mapping.xlsx
+++ b/TS2_mapping.xlsx
@@ -4224,7 +4224,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>無資料</t>
         </is>
       </c>
     </row>

--- a/TS2_mapping.xlsx
+++ b/TS2_mapping.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/TS2_mapping.xlsx
+++ b/TS2_mapping.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/TS2_mapping.xlsx
+++ b/TS2_mapping.xlsx
@@ -10648,17 +10648,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>無資料</t>
+          <t>63565151090012</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>無資料</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">

--- a/TS2_mapping.xlsx
+++ b/TS2_mapping.xlsx
@@ -9598,7 +9598,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">

--- a/TS2_mapping.xlsx
+++ b/TS2_mapping.xlsx
@@ -6031,7 +6031,8 @@
         <is>
           <t xml:space="preserve">Re-do Flytake
 After cleaning, ADST measurement was performed, but the failure symptom remained unchanged
-22-Sep : Inspect ADST / FAU36 remating / FBK </t>
+22-Sep : Inspect ADST / FAU36 remating / FBK 
+01-Oct : Fail on high OE_loss. According to the guidance, if cannot be repaired in other ways, the CSM shall be replaced </t>
         </is>
       </c>
       <c r="Q79" t="inlineStr"/>

--- a/TS2_mapping.xlsx
+++ b/TS2_mapping.xlsx
@@ -6121,7 +6121,8 @@
         <is>
           <t xml:space="preserve">PASS AOT - &gt; ELS cage damage; need to replace ELS cage
 27-Sep: Replaced ELS board; now failed on MST device on ELS 2
-Verify voltage indication on the unit; summarize the history of the unit  </t>
+Verify voltage indication on the unit; summarize the history of the unit  
+01-Oct : ICT Pass - &gt; next promote to JTAG  </t>
         </is>
       </c>
       <c r="Q80" t="inlineStr"/>

--- a/TS2_mapping.xlsx
+++ b/TS2_mapping.xlsx
@@ -6122,7 +6122,8 @@
           <t xml:space="preserve">PASS AOT - &gt; ELS cage damage; need to replace ELS cage
 27-Sep: Replaced ELS board; now failed on MST device on ELS 2
 Verify voltage indication on the unit; summarize the history of the unit  
-01-Oct : ICT Pass - &gt; next promote to JTAG  </t>
+01-Oct : ICT Pass - &gt; next promote to JTAG  
+Suspected as Sagita berun </t>
         </is>
       </c>
       <c r="Q80" t="inlineStr"/>

--- a/TS2_mapping.xlsx
+++ b/TS2_mapping.xlsx
@@ -9068,7 +9068,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>無資料</t>
+          <t>63565151080011</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">

--- a/TS2_mapping.xlsx
+++ b/TS2_mapping.xlsx
@@ -11588,7 +11588,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>無資料</t>
+          <t>63865156210002</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
